--- a/docs/【田島組】ガントチャート_（仮）.xlsx
+++ b/docs/【田島組】ガントチャート_（仮）.xlsx
@@ -1904,7 +1904,7 @@
         <v>46173.625</v>
       </c>
       <c r="E14" s="18">
-        <v>46179.625</v>
+        <v>46177.625</v>
       </c>
       <c r="F14" s="19">
         <v>0</v>
@@ -5357,7 +5357,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D33CA17A-07CC-4463-AB90-D13646C396A1}</x14:id>
+          <x14:id>{D1B7AE9C-7F5E-4479-9527-9D0AF1222D3A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5371,7 +5371,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D33CA17A-07CC-4463-AB90-D13646C396A1}">
+          <x14:cfRule type="dataBar" id="{D1B7AE9C-7F5E-4479-9527-9D0AF1222D3A}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
